--- a/staff_application_forms/021_summer_activities_staff_application_form--staff_application_forms.xlsx
+++ b/staff_application_forms/021_summer_activities_staff_application_form--staff_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'summer_camp_counselor',_'label':_'summer_camp_counselor'}</t>
+          <t>summer_camp_counselor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Summer Camp Counselor', 'label': 'Summer Camp Counselor'}</t>
+          <t>Summer Camp Counselor</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'activity_leader',_'label':_'activity_leader'}</t>
+          <t>activity_leader</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Activity Leader', 'label': 'Activity Leader'}</t>
+          <t>Activity Leader</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'program_director',_'label':_'program_director'}</t>
+          <t>program_director</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Program Director', 'label': 'Program Director'}</t>
+          <t>Program Director</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'saturday',_'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Saturday', 'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'sunday',_'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Sunday', 'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'weekday',_'label':_'weekday'}</t>
+          <t>weekday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Weekday', 'label': 'Weekday'}</t>
+          <t>Weekday</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'morning',_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Morning', 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'afternoon',_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Afternoon', 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'evening',_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Evening', 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'morning',_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Morning', 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'afternoon',_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Afternoon', 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'evening',_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Evening', 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'first_aid',_'label':_'first_aid'}</t>
+          <t>first_aid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'First Aid', 'label': 'First Aid'}</t>
+          <t>First Aid</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'emergency_response',_'label':_'emergency_response'}</t>
+          <t>emergency_response</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Emergency Response', 'label': 'Emergency Response'}</t>
+          <t>Emergency Response</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'cpr',_'label':_'cpr'}</t>
+          <t>cpr</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'CPR', 'label': 'CPR'}</t>
+          <t>CPR</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'wilderness_first_aid',_'label':_'wilderness_first_aid'}</t>
+          <t>wilderness_first_aid</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Wilderness First Aid', 'label': 'Wilderness First Aid'}</t>
+          <t>Wilderness First Aid</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'water_safety',_'label':_'water_safety'}</t>
+          <t>water_safety</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Water Safety', 'label': 'Water Safety'}</t>
+          <t>Water Safety</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'wfa',_'label':_'wfa'}</t>
+          <t>wfa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'WFA', 'label': 'WFA'}</t>
+          <t>WFA</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'lifeguard',_'label':_'lifeguard'}</t>
+          <t>lifeguard</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Lifeguard', 'label': 'Lifeguard'}</t>
+          <t>Lifeguard</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'first_aid',_'label':_'first_aid'}</t>
+          <t>first_aid</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'First Aid', 'label': 'First Aid'}</t>
+          <t>First Aid</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'emergency_responder',_'label':_'emergency_responder'}</t>
+          <t>emergency_responder</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Emergency Responder', 'label': 'Emergency Responder'}</t>
+          <t>Emergency Responder</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'water_safety',_'label':_'water_safety'}</t>
+          <t>water_safety</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Water Safety', 'label': 'Water Safety'}</t>
+          <t>Water Safety</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'bachelor',_'label':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Bachelor', 'label': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'master',_'label':_'master'}</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Master', 'label': 'Master'}</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'doctorate',_'label':_'doctorate'}</t>
+          <t>doctorate</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Doctorate', 'label': 'Doctorate'}</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'english',_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'English', 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'spanish',_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish', 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'french',_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'French', 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'beginner',_'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Beginner', 'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'intermediate',_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Intermediate', 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'advanced',_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Advanced', 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'youth_program_director',_'label':_'youth_program_director'}</t>
+          <t>youth_program_director</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Youth Program Director', 'label': 'Youth Program Director'}</t>
+          <t>Youth Program Director</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'program_director',_'label':_'program_director'}</t>
+          <t>program_director</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Program Director', 'label': 'Program Director'}</t>
+          <t>Program Director</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'counselor-in-training',_'label':_'counselor-in-training'}</t>
+          <t>counselor-in-training</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Counselor-in-Training', 'label': 'Counselor-in-Training'}</t>
+          <t>Counselor-in-Training</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'full-time',_'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Full-time', 'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'part-time',_'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Part-time', 'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'full',_'label':_'full'}</t>
+          <t>full</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Full', 'label': 'Full'}</t>
+          <t>Full</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'part',_'label':_'part'}</t>
+          <t>part</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Part', 'label': 'Part'}</t>
+          <t>Part</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'employee',_'label':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Employee', 'label': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'volunteer',_'label':_'volunteer'}</t>
+          <t>volunteer</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Volunteer', 'label': 'Volunteer'}</t>
+          <t>Volunteer</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'parent',_'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Parent', 'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'spouse',_'label':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'Spouse', 'label': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
